--- a/artfynd/A 25076-2026 artfynd.xlsx
+++ b/artfynd/A 25076-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80986481</v>
+        <v>137417007</v>
       </c>
       <c r="B20" t="n">
-        <v>92208</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,37 +2527,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tievavuoma, Nb</t>
+          <t>Tjevavuoma, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>852602</v>
+        <v>852811</v>
       </c>
       <c r="R20" t="n">
-        <v>7527712</v>
+        <v>7527914</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2581,12 +2585,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på den övre delen av stammen och ett färskt längre ner till vänster</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2601,27 +2620,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986481</t>
+          <t>https://artportalen.se/Sighting/137417007</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80986483</v>
+        <v>137417008</v>
       </c>
       <c r="B21" t="n">
-        <v>92208</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,37 +2648,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tievavuoma, Nb</t>
+          <t>Tjevavuoma, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>852598</v>
+        <v>852750</v>
       </c>
       <c r="R21" t="n">
-        <v>7527712</v>
+        <v>7528026</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2683,12 +2703,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,27 +2738,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986483</t>
+          <t>https://artportalen.se/Sighting/137417008</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>82698723</v>
+        <v>137417009</v>
       </c>
       <c r="B22" t="n">
-        <v>92157</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,40 +2766,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1102</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tievavuoma, Nb</t>
+          <t>Tjevavuoma, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>852602</v>
+        <v>852818</v>
       </c>
       <c r="R22" t="n">
-        <v>7527726</v>
+        <v>7527940</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,12 +2821,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,44 +2850,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82698723</t>
+          <t>https://artportalen.se/Sighting/137417009</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80986487</v>
+        <v>137417004</v>
       </c>
       <c r="B23" t="n">
-        <v>91905</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,37 +2884,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tievavuoma, Nb</t>
+          <t>Tjevavuoma, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>852596</v>
+        <v>853181</v>
       </c>
       <c r="R23" t="n">
-        <v>7527709</v>
+        <v>7527607</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2901,12 +2939,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2921,27 +2974,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986487</t>
+          <t>https://artportalen.se/Sighting/137417004</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80986489</v>
+        <v>137417014</v>
       </c>
       <c r="B24" t="n">
-        <v>91905</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2949,37 +3002,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tievavuoma, Nb</t>
+          <t>Tjevavuoma, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>852565</v>
+        <v>853181</v>
       </c>
       <c r="R24" t="n">
-        <v>7527715</v>
+        <v>7527550</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3003,12 +3057,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3023,27 +3092,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986489</t>
+          <t>https://artportalen.se/Sighting/137417014</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>80986503</v>
+        <v>80986481</v>
       </c>
       <c r="B25" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3051,21 +3120,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3078,7 +3147,7 @@
         <v>852602</v>
       </c>
       <c r="R25" t="n">
-        <v>7527726</v>
+        <v>7527712</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,22 +3199,22 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986503</t>
+          <t>https://artportalen.se/Sighting/80986481</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80986532</v>
+        <v>80986483</v>
       </c>
       <c r="B26" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,21 +3222,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3177,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>852511</v>
+        <v>852598</v>
       </c>
       <c r="R26" t="n">
-        <v>7527920</v>
+        <v>7527712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,12 +3276,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3238,16 +3307,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986532</t>
+          <t>https://artportalen.se/Sighting/80986483</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>80986473</v>
+        <v>82698723</v>
       </c>
       <c r="B27" t="n">
-        <v>91909</v>
+        <v>92157</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,34 +3324,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tievavuoma, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>852466</v>
+        <v>852602</v>
       </c>
       <c r="R27" t="n">
-        <v>7527604</v>
+        <v>7527726</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,12 +3381,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2019-09-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
+          <t>2019-09-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3323,8 +3395,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3340,16 +3423,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986473</t>
+          <t>https://artportalen.se/Sighting/82698723</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80986475</v>
+        <v>80986487</v>
       </c>
       <c r="B28" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,21 +3440,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3464,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>852801</v>
+        <v>852596</v>
       </c>
       <c r="R28" t="n">
-        <v>7527576</v>
+        <v>7527709</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,16 +3525,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986475</t>
+          <t>https://artportalen.se/Sighting/80986487</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>80986479</v>
+        <v>80986489</v>
       </c>
       <c r="B29" t="n">
-        <v>92369</v>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,21 +3542,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3483,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>852801</v>
+        <v>852565</v>
       </c>
       <c r="R29" t="n">
-        <v>7527579</v>
+        <v>7527715</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,16 +3627,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986479</t>
+          <t>https://artportalen.se/Sighting/80986489</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80986498</v>
+        <v>80986503</v>
       </c>
       <c r="B30" t="n">
-        <v>83173</v>
+        <v>91905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3561,21 +3644,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3585,10 +3668,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>852446</v>
+        <v>852602</v>
       </c>
       <c r="R30" t="n">
-        <v>7527595</v>
+        <v>7527726</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,22 +3723,22 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986498</t>
+          <t>https://artportalen.se/Sighting/80986503</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>80986558</v>
+        <v>80986532</v>
       </c>
       <c r="B31" t="n">
-        <v>83173</v>
+        <v>91905</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3746,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3770,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>852617</v>
+        <v>852511</v>
       </c>
       <c r="R31" t="n">
-        <v>7527843</v>
+        <v>7527920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,38 +3831,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80986558</t>
+          <t>https://artportalen.se/Sighting/80986532</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>80986485</v>
+        <v>80986473</v>
       </c>
       <c r="B32" t="n">
-        <v>92292</v>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3872,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>852560</v>
+        <v>852466</v>
       </c>
       <c r="R32" t="n">
-        <v>7527709</v>
+        <v>7527604</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,7 +3933,869 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/80986473</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>80986475</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tievavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>852801</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7527576</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80986475</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>80986479</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tievavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>852801</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7527579</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80986479</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80986498</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tievavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>852446</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7527595</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80986498</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>80986558</v>
+      </c>
+      <c r="B36" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tievavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>852617</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7527843</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80986558</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>80986485</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tievavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>852560</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7527709</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/80986485</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137417011</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tjevavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>852981</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7527641</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137417011</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137417013</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tjevavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>852861</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7527634</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137417013</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137417006</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58198</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tjevavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>853075</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7527694</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137417006</t>
         </is>
       </c>
     </row>
@@ -3887,6 +4832,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25076-2026 artfynd.xlsx
+++ b/artfynd/A 25076-2026 artfynd.xlsx
@@ -2519,7 +2519,7 @@
         <v>137417007</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137417008</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>137417009</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>137417004</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>137417014</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>137417011</v>
       </c>
       <c r="B38" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137417013</v>
       </c>
       <c r="B39" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>137417006</v>
       </c>
       <c r="B40" t="n">
-        <v>58198</v>
+        <v>58201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
